--- a/data/marcas.xlsx
+++ b/data/marcas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>SMELL FRESH</t>
+  </si>
+  <si>
+    <t>ALHAYAA</t>
   </si>
 </sst>
 </file>
@@ -667,6 +670,9 @@
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">

--- a/data/marcas.xlsx
+++ b/data/marcas.xlsx
@@ -33,15 +33,9 @@
     <t>NOSOTRAS</t>
   </si>
   <si>
-    <t>919</t>
-  </si>
-  <si>
     <t>ISSUE</t>
   </si>
   <si>
-    <t>LEAU</t>
-  </si>
-  <si>
     <t>ALGABO</t>
   </si>
   <si>
@@ -220,6 +214,12 @@
   </si>
   <si>
     <t>ALHAYAA</t>
+  </si>
+  <si>
+    <t>919 Y LEAUVIVE</t>
+  </si>
+  <si>
+    <t>EASY CLEAN</t>
   </si>
 </sst>
 </file>
@@ -599,7 +599,7 @@
   <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -631,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -639,7 +639,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -647,7 +647,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -655,7 +655,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -663,7 +663,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -671,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -679,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -687,7 +687,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -695,7 +695,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -711,7 +711,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -727,7 +727,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -735,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -743,7 +743,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -759,7 +759,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -767,7 +767,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -775,7 +775,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -783,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -791,7 +791,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -799,7 +799,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -807,7 +807,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -815,7 +815,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -823,7 +823,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -831,7 +831,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -839,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -847,7 +847,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -855,7 +855,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -863,7 +863,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -871,7 +871,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -879,7 +879,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -887,7 +887,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -895,7 +895,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -903,7 +903,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -911,7 +911,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -919,7 +919,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -927,7 +927,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -935,7 +935,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -943,7 +943,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -951,7 +951,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -959,7 +959,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -975,7 +975,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -983,7 +983,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -991,7 +991,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -999,7 +999,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1007,7 +1007,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1031,7 +1031,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1039,7 +1039,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1047,7 +1047,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1055,7 +1055,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1063,7 +1063,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1071,7 +1071,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1079,7 +1079,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1087,7 +1087,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1139,7 +1139,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1147,7 +1147,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -1163,7 +1163,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B7 A10:B44 A8 A9 A46:B46 A45 A48:B50 A47 A52:B60 A51 A63:B63 A61 A62 A66:B66 A64 A65 A69:B70 A67 A68 A72 A71" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B3 A10:B44 A8 A9 A46:B46 A45 A48:B50 A47 A52:B60 A51 A63:B63 A61 A62 A66:B66 A64 A65 A69:B70 A67 A68 A72 A71 A5:B5 A4 A7 A6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>